--- a/ISO-9001-2026/ISO-9001-2026-modelo.xlsx
+++ b/ISO-9001-2026/ISO-9001-2026-modelo.xlsx
@@ -771,7 +771,7 @@
     <t xml:space="preserve">Separar as oportunidades da SWOT numa lista própria, com ação e prazo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Troca do sistema de pedidos sem plano, em abril de 2027</t>
+    <t xml:space="preserve">Lançamento da pizza vegana planejado pelo projeto P-03; a atualização de versão do sistema de pedidos, em abril de 2027, foi feita sem plano</t>
   </si>
   <si>
     <t xml:space="preserve">Criar uma rotina simples de planejar mudanças no sistema.</t>
@@ -822,7 +822,7 @@
     <t xml:space="preserve">Política revisada com a SWOT e o objetivo O4</t>
   </si>
   <si>
-    <t xml:space="preserve">Riscos C1 a C8 e oportunidades O1 a O4 em listas separadas, desde 2026</t>
+    <t xml:space="preserve">Riscos C1 a C8 e quatro oportunidades em listas separadas, desde 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Procedimento de mudanças do sistema, com plano, comunicação e análise do efeito.</t>
@@ -1450,11 +1450,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="91391338"/>
-        <c:axId val="62688240"/>
+        <c:axId val="8158119"/>
+        <c:axId val="76668677"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="91391338"/>
+        <c:axId val="8158119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1486,7 +1486,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62688240"/>
+        <c:crossAx val="76668677"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1494,7 +1494,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62688240"/>
+        <c:axId val="76668677"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1534,7 +1534,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91391338"/>
+        <c:crossAx val="8158119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -4682,7 +4682,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>

--- a/ISO-9001-2026/ISO-9001-2026-modelo.xlsx
+++ b/ISO-9001-2026/ISO-9001-2026-modelo.xlsx
@@ -771,7 +771,7 @@
     <t xml:space="preserve">Separar as oportunidades da SWOT numa lista própria, com ação e prazo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lançamento da pizza vegana planejado pelo projeto P-03; a atualização de versão do sistema de pedidos, em abril de 2027, foi feita sem plano</t>
+    <t xml:space="preserve">Inclusão do salão no sistema planejada na análise crítica de 14/12/2026, com responsável e prazo; a atualização de versão do sistema de pedidos, em abril de 2027, foi feita sem plano</t>
   </si>
   <si>
     <t xml:space="preserve">Criar uma rotina simples de planejar mudanças no sistema.</t>
@@ -1450,11 +1450,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="8158119"/>
-        <c:axId val="76668677"/>
+        <c:axId val="72894394"/>
+        <c:axId val="47002796"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8158119"/>
+        <c:axId val="72894394"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1486,7 +1486,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76668677"/>
+        <c:crossAx val="47002796"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1494,7 +1494,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="76668677"/>
+        <c:axId val="47002796"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1534,7 +1534,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8158119"/>
+        <c:crossAx val="72894394"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -4682,7 +4682,7 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
